--- a/technology_surveys/003_public_perception_of_health_ai_tools_survey--technology_surveys.xlsx
+++ b/technology_surveys/003_public_perception_of_health_ai_tools_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'developer',_'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Developer', 'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'manager',_'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Manager', 'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'data_scientist',_'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Data Scientist', 'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': True, 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': False, 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Daily', 'value': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Weekly', 'value': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Monthly', 'value': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Rarely', 'value': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'data_analysis',_'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Data Analysis', 'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'predictive_modeling',_'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Predictive Modeling', 'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'personalized_medicine',_'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Personalized Medicine', 'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'other_(please_specify)',_'value':_'4'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Other (please specify)', 'value': '4'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'none',_'value':_'5'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'None', 'value': '5'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'very_accurate',_'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Very accurate', 'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'somewhat_accurate',_'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Somewhat accurate', 'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'not_very_accurate',_'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Not very accurate', 'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'not_at_all_accurate',_'value':_'4'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Not at all accurate', 'value': '4'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'unsure',_'value':_'5'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Unsure', 'value': '5'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'very_easy',_'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Very easy', 'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'somewhat_easy',_'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Somewhat easy', 'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'not_very_easy',_'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Not very easy', 'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'not_at_all_easy',_'value':_'4'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Not at all easy', 'value': '4'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'unsure',_'value':_'5'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Unsure', 'value': '5'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': True, 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': False, 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'improved_accuracy',_'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Improved accuracy', 'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'enhanced_features',_'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Enhanced features', 'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'increased_efficiency',_'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Increased efficiency', 'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'personalized_recommendations',_'value':_'4'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Personalized recommendations', 'value': '4'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
